--- a/Test-Execution-Reports/OrangeHRM-Test report.xlsx
+++ b/Test-Execution-Reports/OrangeHRM-Test report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mr MaD\Desktop\temp\git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80EAB82E-CA60-4357-868F-BFDD9FFDE0B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC485FE5-3D4C-44C6-89D0-35F0336C51A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{5D3ED2AA-EDDA-458F-A1C3-42AB507466B8}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="123">
   <si>
     <t>TC ID</t>
   </si>
@@ -327,6 +327,9 @@
     <t>Actual Result</t>
   </si>
   <si>
+    <t>Fail</t>
+  </si>
+  <si>
     <t>TC21</t>
   </si>
   <si>
@@ -430,13 +433,31 @@
   </si>
   <si>
     <t>Matching user record is displayed in the results</t>
+  </si>
+  <si>
+    <t>Edit and save existing employee name</t>
+  </si>
+  <si>
+    <t>1. Open an employee record
+2. Go to name tab
+3. Change name
+4. Click Save</t>
+  </si>
+  <si>
+    <t>Updated name saved and reflected immediately on the profile</t>
+  </si>
+  <si>
+    <t>TC26</t>
+  </si>
+  <si>
+    <t>PIM "Add Employee" form successfully saves records containing special characters and numbers in the First Name and Last Name fields without validation.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -447,6 +468,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -470,7 +498,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -480,6 +508,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -579,53 +612,61 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Bad" xfId="2" builtinId="27"/>
     <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -945,7 +986,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69140E08-8C1B-4476-BC10-E518D818DDCC}">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultColWidth="80.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
@@ -1005,7 +1046,7 @@
       <c r="G2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="9" t="s">
         <v>81</v>
       </c>
     </row>
@@ -1031,7 +1072,7 @@
       <c r="G3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="9" t="s">
         <v>81</v>
       </c>
     </row>
@@ -1057,7 +1098,7 @@
       <c r="G4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="9" t="s">
         <v>81</v>
       </c>
     </row>
@@ -1083,7 +1124,7 @@
       <c r="G5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="9" t="s">
         <v>81</v>
       </c>
     </row>
@@ -1109,7 +1150,7 @@
       <c r="G6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="9" t="s">
         <v>81</v>
       </c>
     </row>
@@ -1135,7 +1176,7 @@
       <c r="G7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="H7" s="9" t="s">
         <v>81</v>
       </c>
     </row>
@@ -1161,7 +1202,7 @@
       <c r="G8" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="9" t="s">
         <v>81</v>
       </c>
     </row>
@@ -1187,7 +1228,7 @@
       <c r="G9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="9" t="s">
         <v>81</v>
       </c>
     </row>
@@ -1199,442 +1240,468 @@
         <v>27</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="D10" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="51" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="D11" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="F10" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="G10" s="4" t="s">
+      <c r="E11" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H10" s="8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="51" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" s="13" t="s">
+      <c r="H11" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="51" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C12" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D12" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E12" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="F12" s="14" t="s">
         <v>51</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>55</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H12" s="8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="51" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+      <c r="H12" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="51" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D14" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E14" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="F13" s="13" t="s">
+      <c r="F14" s="14" t="s">
         <v>59</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>63</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H14" s="8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="51" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
+      <c r="H14" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H15" s="8" t="s">
+      <c r="B15" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H15" s="9" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="51" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="10" t="s">
         <v>56</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>65</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="51" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
         <v>60</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>65</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="51" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="10" t="s">
         <v>64</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>65</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="51" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
         <v>69</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>65</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H19" s="8" t="s">
+      <c r="H19" s="9" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E20" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="F20" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="B21" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="C21" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="E20" s="10" t="s">
+      <c r="D21" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="F20" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="C21" s="10" t="s">
+      <c r="E21" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="D21" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>96</v>
+      <c r="F21" s="11" t="s">
+        <v>94</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H21" s="8" t="s">
+      <c r="H21" s="9" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="C22" s="10" t="s">
+      <c r="A22" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="E22" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="F22" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="C23" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="E22" s="10" t="s">
+      <c r="D23" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="F22" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="G22" s="4" t="s">
+      <c r="E23" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="G23" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H22" s="8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D23" s="10" t="s">
+      <c r="H23" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="C24" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="E23" s="10" t="s">
+      <c r="D24" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="F23" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="G23" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
+      <c r="E24" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="G24" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="G24" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="H24" s="8" t="s">
+      <c r="H24" s="9" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>27</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D25" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="G25" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="D26" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="F25" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>112</v>
+      <c r="E26" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>109</v>
       </c>
       <c r="G26" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H26" s="8" t="s">
+      <c r="H26" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H27" s="9" t="s">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>